--- a/DECEMBER/Outstanding Kitchen/Surya Cipta Niaga December.xlsx
+++ b/DECEMBER/Outstanding Kitchen/Surya Cipta Niaga December.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,12 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>DATE</t>
   </si>
@@ -62,14 +66,23 @@
     <t>TOP SIDE CAP OFF AA6-7</t>
   </si>
   <si>
+    <t>PAID</t>
+  </si>
+  <si>
     <t>STRIPLOIN ICHI BROWN</t>
+  </si>
+  <si>
+    <t>2512/FK-2109</t>
+  </si>
+  <si>
+    <t>TOP SIDE BLACK ANGUS GF ONYX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -77,6 +90,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]d\-mmm\-yyyy;@"/>
     <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="179" formatCode="dd\-mmm\-yy"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -280,7 +294,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,17 +841,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -921,16 +932,16 @@
     <xf numFmtId="177" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1228,7 +1239,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_476A4EDDA31445A5A86303E8D9468ECE" descr="WhatsApp Image 2025-12-05 at 22.22.25_e586c937"/>
+        <xdr:cNvPr id="3" name="ID_476A4EDDA31445A5A86303E8D9468ECE" descr="WhatsApp Image 2025-12-05 at 22.22.25_e586c937"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1244,6 +1255,45 @@
         <a:xfrm rot="16200000">
           <a:off x="7549515" y="-229235"/>
           <a:ext cx="1480820" cy="2396490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22542</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2963862</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>976312</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_26F8ADC788744EA38C6F5D37F2623152" descr="PHOTO-2025-12-22-17-17-30"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect t="3226" b="7141"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="7593965" y="1278255"/>
+          <a:ext cx="1939925" cy="2941320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1516,186 +1566,203 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="19" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="28.859375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.4296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5546875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="18.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.859375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.4296875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.859375" customWidth="1"/>
+    <col min="4" max="4" width="25.4296875" customWidth="1"/>
+    <col min="5" max="5" width="36.5546875" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.859375" customWidth="1"/>
+    <col min="9" max="9" width="15.4296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="1" ht="16" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="60" customHeight="1" spans="1:9">
-      <c r="A2" s="7">
+    <row r="2" customFormat="1" ht="60" customHeight="1" spans="1:9">
+      <c r="A2" s="6">
         <v>45995</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>23.74</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="22">
+      <c r="E2" s="20"/>
+      <c r="F2" s="21">
         <v>250000</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="22">
         <f t="shared" ref="G2:G6" si="0">D2*F2</f>
         <v>5935000</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="22">
         <f>SUM(G2:G3)</f>
         <v>7717000</v>
       </c>
-      <c r="I2" s="31">
-        <v>45972</v>
+      <c r="I2" s="30" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="60" customHeight="1" spans="1:9">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="10">
+    <row r="3" customFormat="1" ht="60" customHeight="1" spans="1:9">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="9">
         <v>9.9</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="22">
+      <c r="E3" s="23"/>
+      <c r="F3" s="21">
         <v>180000</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="22">
         <f t="shared" si="0"/>
         <v>1782000</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="32"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="31"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="55" customHeight="1" spans="1:9">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="23">
+    <row r="4" customFormat="1" ht="80" customHeight="1" spans="1:9">
+      <c r="A4" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9">
+        <v>9.16</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21">
+        <v>250000</v>
+      </c>
+      <c r="G4" s="22">
+        <f t="shared" si="0"/>
+        <v>2290000</v>
+      </c>
+      <c r="H4" s="22">
+        <f>SUM(G4:G5)</f>
+        <v>4072000</v>
+      </c>
+      <c r="I4" s="32">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="80" customHeight="1" spans="1:9">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="9">
+        <v>9.9</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="21">
+        <v>180000</v>
+      </c>
+      <c r="G5" s="22">
+        <f t="shared" si="0"/>
+        <v>1782000</v>
+      </c>
+      <c r="H5" s="24"/>
+      <c r="I5" s="33"/>
+    </row>
+    <row r="6" customFormat="1" ht="60" customHeight="1" spans="1:9">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="23">
-        <f>SUM(G4:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="33"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="55" customHeight="1" spans="1:9">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="34"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="60" customHeight="1" spans="1:9">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <f>SUM(D6*F6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="28"/>
+      <c r="I6" s="27"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="60" customHeight="1" spans="1:9">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
+    <row r="7" customFormat="1" ht="60" customHeight="1" spans="1:9">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="180" customHeight="1" spans="1:9">
-      <c r="A8" s="18"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="23">
+    <row r="8" customFormat="1" ht="180" customHeight="1" spans="1:9">
+      <c r="A8" s="17"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="22">
         <f>D8*F8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <f>SUM(D8*F8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="28"/>
+      <c r="I8" s="27"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="26" spans="1:9">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="1" ht="26" spans="1:9">
+      <c r="A9" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="29">
-        <f>SUM(H2:H8)</f>
-        <v>7717000</v>
-      </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="35"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="28">
+        <f>SUM(H4:H8)</f>
+        <v>4072000</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="15">
